--- a/data/trans_orig/IP16B10-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16B10-Clase-trans_orig.xlsx
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>874</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2728</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,3%</t>
         </is>
       </c>
     </row>
